--- a/hall/resources/sample/EmployeeSkillConfig.xlsx
+++ b/hall/resources/sample/EmployeeSkillConfig.xlsx
@@ -27,12 +27,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="32">
   <si>
     <t>ID</t>
   </si>
   <si>
-    <t>技能</t>
+    <t>品质</t>
+  </si>
+  <si>
+    <t>类型</t>
+  </si>
+  <si>
+    <t>序列</t>
+  </si>
+  <si>
+    <t>技能名称多语言</t>
   </si>
   <si>
     <t>技能名称</t>
@@ -53,7 +62,16 @@
     <t>id</t>
   </si>
   <si>
-    <t>Skill</t>
+    <t>Quality</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>Index</t>
+  </si>
+  <si>
+    <t>SkillName</t>
   </si>
   <si>
     <t>Modifier</t>
@@ -735,7 +753,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -745,11 +763,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1276,15 +1300,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="3" width="14.25" customWidth="1"/>
-    <col min="4" max="4" width="19.5" customWidth="1"/>
-    <col min="5" max="5" width="20.625" customWidth="1"/>
+    <col min="5" max="6" width="14.25" customWidth="1"/>
+    <col min="7" max="7" width="19.5" customWidth="1"/>
+    <col min="8" max="8" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1300,220 +1324,1352 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1"/>
+        <v>8</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="D2" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>8</v>
+      </c>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="1"/>
+        <v>11</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="D3" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>14</v>
+      </c>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="2"/>
-    </row>
-    <row r="5" spans="1:10">
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="2"/>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
-        <v>1</v>
+        <f>C5*10000+B5*100+D5</f>
+        <v>100101</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="C5" s="1">
+        <v>10</v>
+      </c>
+      <c r="D5" s="3">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1">
+        <v>4051001</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
+        <f>C6*10000+B6*100+D6</f>
+        <v>100102</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1">
+        <v>10</v>
+      </c>
+      <c r="D6" s="3">
         <v>2</v>
       </c>
-      <c r="B6" s="1">
+      <c r="E6" s="1">
+        <v>4051002</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1">
+        <f>C7*10000+B7*100+D7</f>
+        <v>100103</v>
+      </c>
+      <c r="B7" s="1">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1">
+        <v>10</v>
+      </c>
+      <c r="D7" s="3">
+        <v>3</v>
+      </c>
+      <c r="E7" s="1">
+        <v>4051003</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1">
+        <f>C8*10000+B8*100+D8</f>
+        <v>100201</v>
+      </c>
+      <c r="B8" s="1">
         <v>2</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="1">
+      <c r="C8" s="1">
+        <v>10</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1">
+        <v>4051001</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="1">
+        <f>C9*10000+B9*100+D9</f>
+        <v>100202</v>
+      </c>
+      <c r="B9" s="1">
+        <v>2</v>
+      </c>
+      <c r="C9" s="1">
+        <v>10</v>
+      </c>
+      <c r="D9" s="1">
+        <v>2</v>
+      </c>
+      <c r="E9" s="1">
+        <v>4051002</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="1">
+        <f>C10*10000+B10*100+D10</f>
+        <v>100203</v>
+      </c>
+      <c r="B10" s="1">
+        <v>2</v>
+      </c>
+      <c r="C10" s="1">
+        <v>10</v>
+      </c>
+      <c r="D10" s="1">
         <v>3</v>
       </c>
-      <c r="B7" s="1">
+      <c r="E10" s="1">
+        <v>4051003</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="1">
+        <f t="shared" ref="A11:A19" si="0">C11*10000+B11*100+D11</f>
+        <v>100301</v>
+      </c>
+      <c r="B11" s="1">
         <v>3</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C11" s="1">
+        <v>10</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1">
+        <v>4051001</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="G11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="H11" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="1">
+    <row r="12" spans="1:8">
+      <c r="A12" s="1">
+        <f t="shared" si="0"/>
+        <v>100302</v>
+      </c>
+      <c r="B12" s="1">
+        <v>3</v>
+      </c>
+      <c r="C12" s="1">
+        <v>10</v>
+      </c>
+      <c r="D12" s="1">
+        <v>2</v>
+      </c>
+      <c r="E12" s="1">
+        <v>4051002</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="1">
+        <f t="shared" si="0"/>
+        <v>100303</v>
+      </c>
+      <c r="B13" s="1">
+        <v>3</v>
+      </c>
+      <c r="C13" s="1">
+        <v>10</v>
+      </c>
+      <c r="D13" s="1">
+        <v>3</v>
+      </c>
+      <c r="E13" s="1">
+        <v>4051003</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="1">
+        <f t="shared" si="0"/>
+        <v>100401</v>
+      </c>
+      <c r="B14" s="1">
         <v>4</v>
       </c>
-      <c r="B8" s="1">
+      <c r="C14" s="1">
+        <v>10</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1">
+        <v>4051001</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="1">
+        <f t="shared" si="0"/>
+        <v>100402</v>
+      </c>
+      <c r="B15" s="1">
         <v>4</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C15" s="1">
+        <v>10</v>
+      </c>
+      <c r="D15" s="1">
+        <v>2</v>
+      </c>
+      <c r="E15" s="1">
+        <v>4051002</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="1">
+      <c r="G15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="1">
+        <f t="shared" si="0"/>
+        <v>100403</v>
+      </c>
+      <c r="B16" s="1">
+        <v>4</v>
+      </c>
+      <c r="C16" s="1">
+        <v>10</v>
+      </c>
+      <c r="D16" s="1">
+        <v>3</v>
+      </c>
+      <c r="E16" s="1">
+        <v>4051003</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="1">
+        <f t="shared" si="0"/>
+        <v>100501</v>
+      </c>
+      <c r="B17" s="1">
         <v>5</v>
       </c>
-      <c r="B9" s="1">
+      <c r="C17" s="1">
+        <v>10</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
+      <c r="E17" s="1">
+        <v>4051001</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="1">
+        <f t="shared" si="0"/>
+        <v>100502</v>
+      </c>
+      <c r="B18" s="1">
         <v>5</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C18" s="1">
+        <v>10</v>
+      </c>
+      <c r="D18" s="1">
+        <v>2</v>
+      </c>
+      <c r="E18" s="1">
+        <v>4051002</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G18" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="1">
-        <v>6</v>
-      </c>
-      <c r="B10" s="1">
-        <v>6</v>
-      </c>
-      <c r="C10" s="1" t="s">
+      <c r="H18" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="1" t="s">
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="1">
+        <f t="shared" si="0"/>
+        <v>100503</v>
+      </c>
+      <c r="B19" s="1">
+        <v>5</v>
+      </c>
+      <c r="C19" s="1">
+        <v>10</v>
+      </c>
+      <c r="D19" s="1">
+        <v>3</v>
+      </c>
+      <c r="E19" s="1">
+        <v>4051003</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="1">
+        <f>C20*10000+B20*100+D20</f>
+        <v>200101</v>
+      </c>
+      <c r="B20" s="1">
+        <v>1</v>
+      </c>
+      <c r="C20" s="1">
+        <v>20</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
+      <c r="E20" s="1">
+        <v>4051004</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G20" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="H20" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="1">
-        <v>7</v>
-      </c>
-      <c r="B11" s="1">
-        <v>7</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="1">
-        <v>8</v>
-      </c>
-      <c r="B12" s="1">
-        <v>8</v>
-      </c>
-      <c r="C12" s="1" t="s">
+    <row r="21" spans="1:8">
+      <c r="A21" s="1">
+        <f>C21*10000+B21*100+D21</f>
+        <v>200102</v>
+      </c>
+      <c r="B21" s="1">
+        <v>1</v>
+      </c>
+      <c r="C21" s="1">
+        <v>20</v>
+      </c>
+      <c r="D21" s="1">
+        <v>2</v>
+      </c>
+      <c r="E21" s="1">
+        <v>4051005</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="1">
+        <f>C22*10000+B22*100+D22</f>
+        <v>200103</v>
+      </c>
+      <c r="B22" s="1">
+        <v>1</v>
+      </c>
+      <c r="C22" s="1">
+        <v>20</v>
+      </c>
+      <c r="D22" s="1">
+        <v>3</v>
+      </c>
+      <c r="E22" s="1">
+        <v>4051006</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G22" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="1">
-        <v>9</v>
-      </c>
-      <c r="B13" s="1">
-        <v>9</v>
-      </c>
-      <c r="C13" s="1" t="s">
+      <c r="H22" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="1" t="s">
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="1">
+        <f t="shared" ref="A23:A34" si="1">C23*10000+B23*100+D23</f>
+        <v>200201</v>
+      </c>
+      <c r="B23" s="1">
+        <v>2</v>
+      </c>
+      <c r="C23" s="1">
+        <v>20</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
+      <c r="E23" s="1">
+        <v>4051004</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="H23" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="I14" s="4"/>
-      <c r="J14" s="3"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="I15" s="4"/>
-      <c r="J15" s="3"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-    </row>
-    <row r="17" spans="9:10">
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-    </row>
-    <row r="18" spans="9:10">
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="1">
+        <f t="shared" si="1"/>
+        <v>200202</v>
+      </c>
+      <c r="B24" s="1">
+        <v>2</v>
+      </c>
+      <c r="C24" s="1">
+        <v>20</v>
+      </c>
+      <c r="D24" s="1">
+        <v>2</v>
+      </c>
+      <c r="E24" s="1">
+        <v>4051005</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="1">
+        <f t="shared" si="1"/>
+        <v>200203</v>
+      </c>
+      <c r="B25" s="1">
+        <v>2</v>
+      </c>
+      <c r="C25" s="1">
+        <v>20</v>
+      </c>
+      <c r="D25" s="1">
+        <v>3</v>
+      </c>
+      <c r="E25" s="1">
+        <v>4051006</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="1">
+        <f t="shared" si="1"/>
+        <v>200301</v>
+      </c>
+      <c r="B26" s="1">
+        <v>3</v>
+      </c>
+      <c r="C26" s="1">
+        <v>20</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
+      <c r="E26" s="1">
+        <v>4051004</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="1">
+        <f t="shared" si="1"/>
+        <v>200302</v>
+      </c>
+      <c r="B27" s="1">
+        <v>3</v>
+      </c>
+      <c r="C27" s="1">
+        <v>20</v>
+      </c>
+      <c r="D27" s="1">
+        <v>2</v>
+      </c>
+      <c r="E27" s="1">
+        <v>4051005</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="1">
+        <f t="shared" si="1"/>
+        <v>200303</v>
+      </c>
+      <c r="B28" s="1">
+        <v>3</v>
+      </c>
+      <c r="C28" s="1">
+        <v>20</v>
+      </c>
+      <c r="D28" s="1">
+        <v>3</v>
+      </c>
+      <c r="E28" s="1">
+        <v>4051006</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="1">
+        <f t="shared" si="1"/>
+        <v>200401</v>
+      </c>
+      <c r="B29" s="1">
+        <v>4</v>
+      </c>
+      <c r="C29" s="1">
+        <v>20</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
+      <c r="E29" s="1">
+        <v>4051004</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="1">
+        <f t="shared" si="1"/>
+        <v>200402</v>
+      </c>
+      <c r="B30" s="1">
+        <v>4</v>
+      </c>
+      <c r="C30" s="1">
+        <v>20</v>
+      </c>
+      <c r="D30" s="1">
+        <v>2</v>
+      </c>
+      <c r="E30" s="1">
+        <v>4051005</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="1">
+        <f t="shared" si="1"/>
+        <v>200403</v>
+      </c>
+      <c r="B31" s="1">
+        <v>4</v>
+      </c>
+      <c r="C31" s="1">
+        <v>20</v>
+      </c>
+      <c r="D31" s="1">
+        <v>3</v>
+      </c>
+      <c r="E31" s="1">
+        <v>4051006</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="1">
+        <f t="shared" si="1"/>
+        <v>200501</v>
+      </c>
+      <c r="B32" s="1">
+        <v>5</v>
+      </c>
+      <c r="C32" s="1">
+        <v>20</v>
+      </c>
+      <c r="D32" s="1">
+        <v>1</v>
+      </c>
+      <c r="E32" s="1">
+        <v>4051004</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
+      <c r="A33" s="1">
+        <f t="shared" si="1"/>
+        <v>200502</v>
+      </c>
+      <c r="B33" s="1">
+        <v>5</v>
+      </c>
+      <c r="C33" s="1">
+        <v>20</v>
+      </c>
+      <c r="D33" s="1">
+        <v>2</v>
+      </c>
+      <c r="E33" s="1">
+        <v>4051005</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
+      <c r="A34" s="1">
+        <f t="shared" si="1"/>
+        <v>200503</v>
+      </c>
+      <c r="B34" s="1">
+        <v>5</v>
+      </c>
+      <c r="C34" s="1">
+        <v>20</v>
+      </c>
+      <c r="D34" s="1">
+        <v>3</v>
+      </c>
+      <c r="E34" s="1">
+        <v>4051006</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
+      <c r="A35" s="1">
+        <f>C35*10000+B35*100+D35</f>
+        <v>300101</v>
+      </c>
+      <c r="B35" s="1">
+        <v>1</v>
+      </c>
+      <c r="C35" s="1">
+        <v>30</v>
+      </c>
+      <c r="D35" s="1">
+        <v>1</v>
+      </c>
+      <c r="E35" s="1">
+        <v>4051007</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
+      <c r="A36" s="1">
+        <f>C36*10000+B36*100+D36</f>
+        <v>300102</v>
+      </c>
+      <c r="B36" s="1">
+        <v>1</v>
+      </c>
+      <c r="C36" s="1">
+        <v>30</v>
+      </c>
+      <c r="D36" s="1">
+        <v>2</v>
+      </c>
+      <c r="E36" s="1">
+        <v>4051008</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L36" s="4"/>
+      <c r="M36" s="4"/>
+    </row>
+    <row r="37" spans="1:13">
+      <c r="A37" s="1">
+        <f>C37*10000+B37*100+D37</f>
+        <v>300103</v>
+      </c>
+      <c r="B37" s="1">
+        <v>1</v>
+      </c>
+      <c r="C37" s="1">
+        <v>30</v>
+      </c>
+      <c r="D37" s="1">
+        <v>3</v>
+      </c>
+      <c r="E37" s="1">
+        <v>4051009</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L37" s="4"/>
+      <c r="M37" s="4"/>
+    </row>
+    <row r="38" spans="1:13">
+      <c r="A38" s="1">
+        <f t="shared" ref="A38:A49" si="2">C38*10000+B38*100+D38</f>
+        <v>300201</v>
+      </c>
+      <c r="B38" s="1">
+        <v>2</v>
+      </c>
+      <c r="C38" s="1">
+        <v>30</v>
+      </c>
+      <c r="D38" s="1">
+        <v>1</v>
+      </c>
+      <c r="E38" s="1">
+        <v>4051007</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L38" s="5"/>
+      <c r="M38" s="4"/>
+    </row>
+    <row r="39" spans="1:13">
+      <c r="A39" s="1">
+        <f t="shared" si="2"/>
+        <v>300202</v>
+      </c>
+      <c r="B39" s="1">
+        <v>2</v>
+      </c>
+      <c r="C39" s="1">
+        <v>30</v>
+      </c>
+      <c r="D39" s="1">
+        <v>2</v>
+      </c>
+      <c r="E39" s="1">
+        <v>4051008</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L39" s="5"/>
+      <c r="M39" s="4"/>
+    </row>
+    <row r="40" spans="1:13">
+      <c r="A40" s="1">
+        <f t="shared" si="2"/>
+        <v>300203</v>
+      </c>
+      <c r="B40" s="1">
+        <v>2</v>
+      </c>
+      <c r="C40" s="1">
+        <v>30</v>
+      </c>
+      <c r="D40" s="1">
+        <v>3</v>
+      </c>
+      <c r="E40" s="1">
+        <v>4051009</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L40" s="5"/>
+      <c r="M40" s="4"/>
+    </row>
+    <row r="41" spans="1:13">
+      <c r="A41" s="1">
+        <f t="shared" si="2"/>
+        <v>300301</v>
+      </c>
+      <c r="B41" s="1">
+        <v>3</v>
+      </c>
+      <c r="C41" s="1">
+        <v>30</v>
+      </c>
+      <c r="D41" s="1">
+        <v>1</v>
+      </c>
+      <c r="E41" s="1">
+        <v>4051007</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L41" s="5"/>
+      <c r="M41" s="4"/>
+    </row>
+    <row r="42" spans="1:13">
+      <c r="A42" s="1">
+        <f t="shared" si="2"/>
+        <v>300302</v>
+      </c>
+      <c r="B42" s="1">
+        <v>3</v>
+      </c>
+      <c r="C42" s="1">
+        <v>30</v>
+      </c>
+      <c r="D42" s="1">
+        <v>2</v>
+      </c>
+      <c r="E42" s="1">
+        <v>4051008</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L42" s="5"/>
+      <c r="M42" s="4"/>
+    </row>
+    <row r="43" spans="1:13">
+      <c r="A43" s="1">
+        <f t="shared" si="2"/>
+        <v>300303</v>
+      </c>
+      <c r="B43" s="1">
+        <v>3</v>
+      </c>
+      <c r="C43" s="1">
+        <v>30</v>
+      </c>
+      <c r="D43" s="1">
+        <v>3</v>
+      </c>
+      <c r="E43" s="1">
+        <v>4051009</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L43" s="5"/>
+      <c r="M43" s="4"/>
+    </row>
+    <row r="44" spans="1:13">
+      <c r="A44" s="1">
+        <f t="shared" si="2"/>
+        <v>300401</v>
+      </c>
+      <c r="B44" s="1">
+        <v>4</v>
+      </c>
+      <c r="C44" s="1">
+        <v>30</v>
+      </c>
+      <c r="D44" s="1">
+        <v>1</v>
+      </c>
+      <c r="E44" s="1">
+        <v>4051007</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L44" s="5"/>
+      <c r="M44" s="4"/>
+    </row>
+    <row r="45" spans="1:13">
+      <c r="A45" s="1">
+        <f t="shared" si="2"/>
+        <v>300402</v>
+      </c>
+      <c r="B45" s="1">
+        <v>4</v>
+      </c>
+      <c r="C45" s="1">
+        <v>30</v>
+      </c>
+      <c r="D45" s="1">
+        <v>2</v>
+      </c>
+      <c r="E45" s="1">
+        <v>4051008</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L45" s="5"/>
+      <c r="M45" s="4"/>
+    </row>
+    <row r="46" spans="1:13">
+      <c r="A46" s="1">
+        <f t="shared" si="2"/>
+        <v>300403</v>
+      </c>
+      <c r="B46" s="1">
+        <v>4</v>
+      </c>
+      <c r="C46" s="1">
+        <v>30</v>
+      </c>
+      <c r="D46" s="1">
+        <v>3</v>
+      </c>
+      <c r="E46" s="1">
+        <v>4051009</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L46" s="5"/>
+      <c r="M46" s="4"/>
+    </row>
+    <row r="47" spans="1:13">
+      <c r="A47" s="1">
+        <f t="shared" si="2"/>
+        <v>300501</v>
+      </c>
+      <c r="B47" s="1">
+        <v>5</v>
+      </c>
+      <c r="C47" s="1">
+        <v>30</v>
+      </c>
+      <c r="D47" s="1">
+        <v>1</v>
+      </c>
+      <c r="E47" s="1">
+        <v>4051007</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L47" s="5"/>
+      <c r="M47" s="4"/>
+    </row>
+    <row r="48" spans="1:13">
+      <c r="A48" s="1">
+        <f t="shared" si="2"/>
+        <v>300502</v>
+      </c>
+      <c r="B48" s="1">
+        <v>5</v>
+      </c>
+      <c r="C48" s="1">
+        <v>30</v>
+      </c>
+      <c r="D48" s="1">
+        <v>2</v>
+      </c>
+      <c r="E48" s="1">
+        <v>4051008</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L48" s="5"/>
+      <c r="M48" s="4"/>
+    </row>
+    <row r="49" spans="1:13">
+      <c r="A49" s="1">
+        <f t="shared" si="2"/>
+        <v>300503</v>
+      </c>
+      <c r="B49" s="1">
+        <v>5</v>
+      </c>
+      <c r="C49" s="1">
+        <v>30</v>
+      </c>
+      <c r="D49" s="1">
+        <v>3</v>
+      </c>
+      <c r="E49" s="1">
+        <v>4051009</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L49" s="5"/>
+      <c r="M49" s="4"/>
+    </row>
+    <row r="50" spans="1:13">
+      <c r="A50" s="6"/>
+      <c r="B50" s="6"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="6"/>
+      <c r="H50" s="6"/>
+      <c r="L50" s="5"/>
+      <c r="M50" s="4"/>
+    </row>
+    <row r="51" spans="1:13">
+      <c r="A51" s="6"/>
+      <c r="B51" s="6"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="6"/>
+      <c r="G51" s="6"/>
+      <c r="H51" s="6"/>
+      <c r="L51" s="5"/>
+      <c r="M51" s="4"/>
+    </row>
+    <row r="52" spans="1:13">
+      <c r="L52" s="4"/>
+      <c r="M52" s="4"/>
+    </row>
+    <row r="53" spans="1:13">
+      <c r="L53" s="4"/>
+      <c r="M53" s="4"/>
+    </row>
+    <row r="54" spans="1:13">
+      <c r="L54" s="4"/>
+      <c r="M54" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hall/resources/sample/EmployeeSkillConfig.xlsx
+++ b/hall/resources/sample/EmployeeSkillConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="44">
   <si>
     <t>ID</t>
   </si>
@@ -83,46 +83,82 @@
     <t>游戏专精</t>
   </si>
   <si>
-    <t>1_10</t>
-  </si>
-  <si>
-    <t>1_30</t>
+    <t>3_20</t>
+  </si>
+  <si>
+    <t>3_200</t>
   </si>
   <si>
     <t>概率心算</t>
   </si>
   <si>
+    <t>3_25</t>
+  </si>
+  <si>
+    <t>3_400</t>
+  </si>
+  <si>
+    <t>幸运女神</t>
+  </si>
+  <si>
+    <t>3_30</t>
+  </si>
+  <si>
+    <t>3_600</t>
+  </si>
+  <si>
+    <t>贴心服务</t>
+  </si>
+  <si>
     <t>5_10</t>
   </si>
   <si>
-    <t>5_30</t>
-  </si>
-  <si>
-    <t>幸运女神</t>
+    <t>5_100</t>
+  </si>
+  <si>
+    <t>微笑治愈</t>
+  </si>
+  <si>
+    <t>5_15</t>
+  </si>
+  <si>
+    <t>5_200</t>
+  </si>
+  <si>
+    <t>洞察需求</t>
+  </si>
+  <si>
+    <t>5_20</t>
+  </si>
+  <si>
+    <t>5_300</t>
+  </si>
+  <si>
+    <t>成本削减</t>
+  </si>
+  <si>
+    <t>4_5</t>
+  </si>
+  <si>
+    <t>4_50</t>
+  </si>
+  <si>
+    <t>统筹全局</t>
   </si>
   <si>
     <t>4_10</t>
   </si>
   <si>
-    <t>4_30</t>
-  </si>
-  <si>
-    <t>贴心服务</t>
-  </si>
-  <si>
-    <t>微笑治愈</t>
-  </si>
-  <si>
-    <t>洞察需求</t>
-  </si>
-  <si>
-    <t>成本削减</t>
-  </si>
-  <si>
-    <t>统筹全局</t>
+    <t>4_100</t>
   </si>
   <si>
     <t>精细管理</t>
+  </si>
+  <si>
+    <t>4_15</t>
+  </si>
+  <si>
+    <t>4_150</t>
   </si>
 </sst>
 </file>
@@ -1394,7 +1430,7 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1">
-        <f>C5*10000+B5*100+D5</f>
+        <f t="shared" ref="A5:A10" si="0">C5*10000+B5*100+D5</f>
         <v>100101</v>
       </c>
       <c r="B5" s="1">
@@ -1421,7 +1457,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1">
-        <f>C6*10000+B6*100+D6</f>
+        <f t="shared" si="0"/>
         <v>100102</v>
       </c>
       <c r="B6" s="1">
@@ -1448,7 +1484,7 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1">
-        <f>C7*10000+B7*100+D7</f>
+        <f t="shared" si="0"/>
         <v>100103</v>
       </c>
       <c r="B7" s="1">
@@ -1475,7 +1511,7 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1">
-        <f>C8*10000+B8*100+D8</f>
+        <f t="shared" si="0"/>
         <v>100201</v>
       </c>
       <c r="B8" s="1">
@@ -1502,7 +1538,7 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1">
-        <f>C9*10000+B9*100+D9</f>
+        <f t="shared" si="0"/>
         <v>100202</v>
       </c>
       <c r="B9" s="1">
@@ -1529,7 +1565,7 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1">
-        <f>C10*10000+B10*100+D10</f>
+        <f t="shared" si="0"/>
         <v>100203</v>
       </c>
       <c r="B10" s="1">
@@ -1556,7 +1592,7 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1">
-        <f t="shared" ref="A11:A19" si="0">C11*10000+B11*100+D11</f>
+        <f t="shared" ref="A11:A22" si="1">C11*10000+B11*100+D11</f>
         <v>100301</v>
       </c>
       <c r="B11" s="1">
@@ -1583,7 +1619,7 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100302</v>
       </c>
       <c r="B12" s="1">
@@ -1610,7 +1646,7 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100303</v>
       </c>
       <c r="B13" s="1">
@@ -1637,7 +1673,7 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100401</v>
       </c>
       <c r="B14" s="1">
@@ -1664,7 +1700,7 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100402</v>
       </c>
       <c r="B15" s="1">
@@ -1691,7 +1727,7 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100403</v>
       </c>
       <c r="B16" s="1">
@@ -1718,7 +1754,7 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100501</v>
       </c>
       <c r="B17" s="1">
@@ -1745,7 +1781,7 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100502</v>
       </c>
       <c r="B18" s="1">
@@ -1772,7 +1808,7 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100503</v>
       </c>
       <c r="B19" s="1">
@@ -1799,7 +1835,7 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1">
-        <f>C20*10000+B20*100+D20</f>
+        <f t="shared" si="1"/>
         <v>200101</v>
       </c>
       <c r="B20" s="1">
@@ -1818,15 +1854,15 @@
         <v>26</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1">
-        <f>C21*10000+B21*100+D21</f>
+        <f t="shared" si="1"/>
         <v>200102</v>
       </c>
       <c r="B21" s="1">
@@ -1842,18 +1878,18 @@
         <v>4051005</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1">
-        <f>C22*10000+B22*100+D22</f>
+        <f t="shared" si="1"/>
         <v>200103</v>
       </c>
       <c r="B22" s="1">
@@ -1869,18 +1905,18 @@
         <v>4051006</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1">
-        <f t="shared" ref="A23:A34" si="1">C23*10000+B23*100+D23</f>
+        <f t="shared" ref="A23:A37" si="2">C23*10000+B23*100+D23</f>
         <v>200201</v>
       </c>
       <c r="B23" s="1">
@@ -1899,15 +1935,15 @@
         <v>26</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>200202</v>
       </c>
       <c r="B24" s="1">
@@ -1923,18 +1959,18 @@
         <v>4051005</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>200203</v>
       </c>
       <c r="B25" s="1">
@@ -1950,18 +1986,18 @@
         <v>4051006</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>200301</v>
       </c>
       <c r="B26" s="1">
@@ -1980,15 +2016,15 @@
         <v>26</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>200302</v>
       </c>
       <c r="B27" s="1">
@@ -2004,18 +2040,18 @@
         <v>4051005</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>200303</v>
       </c>
       <c r="B28" s="1">
@@ -2031,18 +2067,18 @@
         <v>4051006</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>200401</v>
       </c>
       <c r="B29" s="1">
@@ -2061,15 +2097,15 @@
         <v>26</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>200402</v>
       </c>
       <c r="B30" s="1">
@@ -2085,18 +2121,18 @@
         <v>4051005</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>200403</v>
       </c>
       <c r="B31" s="1">
@@ -2112,18 +2148,18 @@
         <v>4051006</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>200501</v>
       </c>
       <c r="B32" s="1">
@@ -2142,15 +2178,15 @@
         <v>26</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33" spans="1:13">
       <c r="A33" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>200502</v>
       </c>
       <c r="B33" s="1">
@@ -2166,18 +2202,18 @@
         <v>4051005</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34" spans="1:13">
       <c r="A34" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>200503</v>
       </c>
       <c r="B34" s="1">
@@ -2193,18 +2229,18 @@
         <v>4051006</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35" spans="1:13">
       <c r="A35" s="1">
-        <f>C35*10000+B35*100+D35</f>
+        <f t="shared" si="2"/>
         <v>300101</v>
       </c>
       <c r="B35" s="1">
@@ -2220,18 +2256,18 @@
         <v>4051007</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="36" spans="1:13">
       <c r="A36" s="1">
-        <f>C36*10000+B36*100+D36</f>
+        <f t="shared" si="2"/>
         <v>300102</v>
       </c>
       <c r="B36" s="1">
@@ -2247,20 +2283,20 @@
         <v>4051008</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="L36" s="4"/>
       <c r="M36" s="4"/>
     </row>
     <row r="37" spans="1:13">
       <c r="A37" s="1">
-        <f>C37*10000+B37*100+D37</f>
+        <f t="shared" si="2"/>
         <v>300103</v>
       </c>
       <c r="B37" s="1">
@@ -2276,20 +2312,20 @@
         <v>4051009</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="L37" s="4"/>
       <c r="M37" s="4"/>
     </row>
     <row r="38" spans="1:13">
       <c r="A38" s="1">
-        <f t="shared" ref="A38:A49" si="2">C38*10000+B38*100+D38</f>
+        <f t="shared" ref="A38:A49" si="3">C38*10000+B38*100+D38</f>
         <v>300201</v>
       </c>
       <c r="B38" s="1">
@@ -2305,20 +2341,20 @@
         <v>4051007</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="L38" s="5"/>
       <c r="M38" s="4"/>
     </row>
     <row r="39" spans="1:13">
       <c r="A39" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>300202</v>
       </c>
       <c r="B39" s="1">
@@ -2334,20 +2370,20 @@
         <v>4051008</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="L39" s="5"/>
       <c r="M39" s="4"/>
     </row>
     <row r="40" spans="1:13">
       <c r="A40" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>300203</v>
       </c>
       <c r="B40" s="1">
@@ -2363,20 +2399,20 @@
         <v>4051009</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="L40" s="5"/>
       <c r="M40" s="4"/>
     </row>
     <row r="41" spans="1:13">
       <c r="A41" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>300301</v>
       </c>
       <c r="B41" s="1">
@@ -2392,20 +2428,20 @@
         <v>4051007</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="L41" s="5"/>
       <c r="M41" s="4"/>
     </row>
     <row r="42" spans="1:13">
       <c r="A42" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>300302</v>
       </c>
       <c r="B42" s="1">
@@ -2421,20 +2457,20 @@
         <v>4051008</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="L42" s="5"/>
       <c r="M42" s="4"/>
     </row>
     <row r="43" spans="1:13">
       <c r="A43" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>300303</v>
       </c>
       <c r="B43" s="1">
@@ -2450,20 +2486,20 @@
         <v>4051009</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="L43" s="5"/>
       <c r="M43" s="4"/>
     </row>
     <row r="44" spans="1:13">
       <c r="A44" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>300401</v>
       </c>
       <c r="B44" s="1">
@@ -2479,20 +2515,20 @@
         <v>4051007</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="L44" s="5"/>
       <c r="M44" s="4"/>
     </row>
     <row r="45" spans="1:13">
       <c r="A45" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>300402</v>
       </c>
       <c r="B45" s="1">
@@ -2508,20 +2544,20 @@
         <v>4051008</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="L45" s="5"/>
       <c r="M45" s="4"/>
     </row>
     <row r="46" spans="1:13">
       <c r="A46" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>300403</v>
       </c>
       <c r="B46" s="1">
@@ -2537,20 +2573,20 @@
         <v>4051009</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="L46" s="5"/>
       <c r="M46" s="4"/>
     </row>
     <row r="47" spans="1:13">
       <c r="A47" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>300501</v>
       </c>
       <c r="B47" s="1">
@@ -2566,20 +2602,20 @@
         <v>4051007</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="L47" s="5"/>
       <c r="M47" s="4"/>
     </row>
     <row r="48" spans="1:13">
       <c r="A48" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>300502</v>
       </c>
       <c r="B48" s="1">
@@ -2595,20 +2631,20 @@
         <v>4051008</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="L48" s="5"/>
       <c r="M48" s="4"/>
     </row>
     <row r="49" spans="1:13">
       <c r="A49" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>300503</v>
       </c>
       <c r="B49" s="1">
@@ -2624,13 +2660,13 @@
         <v>4051009</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="L49" s="5"/>
       <c r="M49" s="4"/>

--- a/hall/resources/sample/EmployeeSkillConfig.xlsx
+++ b/hall/resources/sample/EmployeeSkillConfig.xlsx
@@ -115,7 +115,7 @@
     <t>int</t>
   </si>
   <si>
-    <t>map&lt;int{_}long&gt;{|}</t>
+    <t>map&lt;int{_}int&gt;{|}</t>
   </si>
   <si>
     <t>id</t>
@@ -1585,7 +1585,6 @@
       <c r="E12" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F12"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
     </row>
@@ -1605,7 +1604,6 @@
       <c r="E13" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F13"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
     </row>

--- a/hall/resources/sample/EmployeeSkillConfig.xlsx
+++ b/hall/resources/sample/EmployeeSkillConfig.xlsx
@@ -95,7 +95,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
   <si>
     <t>ID</t>
   </si>
@@ -133,18 +133,12 @@
     <t>游戏专精</t>
   </si>
   <si>
-    <t>1_20</t>
-  </si>
-  <si>
     <t>1_200</t>
   </si>
   <si>
     <t>概率心算</t>
   </si>
   <si>
-    <t>1_25</t>
-  </si>
-  <si>
     <t>1_400</t>
   </si>
   <si>
@@ -154,24 +148,15 @@
     <t>1_10</t>
   </si>
   <si>
-    <t>1_600</t>
-  </si>
-  <si>
     <t>贴心服务</t>
   </si>
   <si>
-    <t>2_10</t>
-  </si>
-  <si>
     <t>2_100</t>
   </si>
   <si>
     <t>微笑治愈</t>
   </si>
   <si>
-    <t>2_15</t>
-  </si>
-  <si>
     <t>2_200</t>
   </si>
   <si>
@@ -181,24 +166,15 @@
     <t>2_20</t>
   </si>
   <si>
-    <t>2_300</t>
-  </si>
-  <si>
     <t>成本削减</t>
   </si>
   <si>
-    <t>11_5</t>
-  </si>
-  <si>
     <t>11_50</t>
   </si>
   <si>
     <t>统筹全局</t>
   </si>
   <si>
-    <t>11_10</t>
-  </si>
-  <si>
     <t>11_100</t>
   </si>
   <si>
@@ -206,9 +182,6 @@
   </si>
   <si>
     <t>11_15</t>
-  </si>
-  <si>
-    <t>11_150</t>
   </si>
 </sst>
 </file>
@@ -1460,11 +1433,9 @@
       <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="1"/>
+      <c r="E5" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1475,13 +1446,11 @@
         <v>4051002</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1492,14 +1461,12 @@
         <v>4051003</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>19</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="E7" s="1"/>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="1">
@@ -1509,13 +1476,11 @@
         <v>4051004</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>21</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="D8" s="1"/>
       <c r="E8" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1526,13 +1491,11 @@
         <v>4051005</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>24</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="D9" s="1"/>
       <c r="E9" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1543,14 +1506,12 @@
         <v>4051006</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>28</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="E10" s="1"/>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="1">
@@ -1560,13 +1521,11 @@
         <v>4051007</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>30</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="D11" s="1"/>
       <c r="E11" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1577,13 +1536,11 @@
         <v>4051008</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>33</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="D12" s="1"/>
       <c r="E12" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
@@ -1596,14 +1553,12 @@
         <v>4051009</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>37</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="E13" s="1"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
     </row>

--- a/hall/resources/sample/EmployeeSkillConfig.xlsx
+++ b/hall/resources/sample/EmployeeSkillConfig.xlsx
@@ -151,13 +151,13 @@
     <t>贴心服务</t>
   </si>
   <si>
-    <t>2_100</t>
+    <t>2_2</t>
   </si>
   <si>
     <t>微笑治愈</t>
   </si>
   <si>
-    <t>2_200</t>
+    <t>2_1</t>
   </si>
   <si>
     <t>洞察需求</t>
@@ -175,7 +175,7 @@
     <t>统筹全局</t>
   </si>
   <si>
-    <t>11_100</t>
+    <t>11_60</t>
   </si>
   <si>
     <t>精细管理</t>
